--- a/Destek_Direc_Seviyeleri.xlsx
+++ b/Destek_Direc_Seviyeleri.xlsx
@@ -62,90 +62,90 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>DİRENÇ YAKIN | GÜÇLÜ YÜKSELİŞ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4/5 (80%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5/5 (100%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASELS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NÖTR | GÜÇLÜ YÜKSELİŞ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKGYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>DİRENÇ YAKIN</x:t>
   </x:si>
   <x:si>
     <x:t>3/5 (60%)</x:t>
   </x:si>
   <x:si>
-    <x:t>AKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DİRENÇ YAKIN | GÜÇLÜ YÜKSELİŞ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5/5 (100%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASELS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASTOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NÖTR | GÜÇLÜ YÜKSELİŞ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
+    <x:t>ENKAI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FROTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUBRF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISCTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
   </x:si>
   <x:si>
     <x:t>PİVOT ÜSTÜ | GÜÇLÜ YÜKSELİŞ</x:t>
   </x:si>
   <x:si>
-    <x:t>EKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENKAI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FROTO</x:t>
+    <x:t>MGROS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PİVOT ALT | GÜÇLÜ YÜKSELİŞ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PGSUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PİVOT ALT</x:t>
   </x:si>
   <x:si>
     <x:t>2/5 (40%)</x:t>
   </x:si>
   <x:si>
-    <x:t>GARAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUBRF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4/5 (80%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISCTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MGROS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PİVOT ALT | GÜÇLÜ YÜKSELİŞ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PGSUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PİVOT ÜSTÜ</x:t>
-  </x:si>
-  <x:si>
     <x:t>SAHOL</x:t>
   </x:si>
   <x:si>
@@ -168,6 +168,9 @@
   </x:si>
   <x:si>
     <x:t>TRALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NÖTR</x:t>
   </x:si>
   <x:si>
     <x:t>TTKOM</x:t>
@@ -582,10 +585,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>17.45</x:v>
+        <x:v>17.46</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>16.51</x:v>
+        <x:v>16.56</x:v>
       </x:c>
       <x:c r="F2" s="0">
         <x:v>17.73</x:v>
@@ -620,10 +623,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>75.75</x:v>
+        <x:v>75.15</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>66.45</x:v>
+        <x:v>68.25</x:v>
       </x:c>
       <x:c r="F3" s="0">
         <x:v>76.15</x:v>
@@ -641,15 +644,15 @@
         <x:v>90.6</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:12">
       <x:c r="A4" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>13</x:v>
@@ -658,36 +661,36 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>362.25</x:v>
+        <x:v>375.5</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>323.25</x:v>
+        <x:v>327.75</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>366.5</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="G4" s="0">
         <x:v>314.75</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>366.5</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>283</x:v>
       </x:c>
       <x:c r="J4" s="0">
-        <x:v>366.5</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:12">
       <x:c r="A5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>13</x:v>
@@ -696,10 +699,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>207.3</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>194.9</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="F5" s="0">
         <x:v>215.7</x:v>
@@ -717,15 +720,15 @@
         <x:v>215.7</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:12">
       <x:c r="A6" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>13</x:v>
@@ -734,36 +737,36 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>726.5</x:v>
+        <x:v>739.5</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>681</x:v>
+        <x:v>683.5</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>739.5</x:v>
+        <x:v>741.5</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>644.5</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>739.5</x:v>
+        <x:v>741.5</x:v>
       </x:c>
       <x:c r="I6" s="0">
         <x:v>607.5</x:v>
       </x:c>
       <x:c r="J6" s="0">
-        <x:v>739.5</x:v>
+        <x:v>741.5</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:12">
       <x:c r="A7" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>13</x:v>
@@ -772,10 +775,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>2002</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>1920</x:v>
+        <x:v>1949</x:v>
       </x:c>
       <x:c r="F7" s="0">
         <x:v>2066</x:v>
@@ -793,15 +796,15 @@
         <x:v>2066</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:12">
       <x:c r="A8" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>13</x:v>
@@ -810,7 +813,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>20.62</x:v>
+        <x:v>20.54</x:v>
       </x:c>
       <x:c r="E8" s="0">
         <x:v>19.12</x:v>
@@ -822,7 +825,7 @@
         <x:v>18.86</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>21.9</x:v>
+        <x:v>21.5</x:v>
       </x:c>
       <x:c r="I8" s="0">
         <x:v>18.86</x:v>
@@ -831,10 +834,10 @@
         <x:v>27.12</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:12">
@@ -848,7 +851,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>95.05</x:v>
+        <x:v>94.9</x:v>
       </x:c>
       <x:c r="E9" s="0">
         <x:v>90.46</x:v>
@@ -869,10 +872,10 @@
         <x:v>102.34</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:12">
@@ -886,31 +889,31 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>29.58</x:v>
+        <x:v>30.46</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>27.94</x:v>
+        <x:v>28.02</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>30.34</x:v>
+        <x:v>30.5</x:v>
       </x:c>
       <x:c r="G10" s="0">
         <x:v>26.78</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>30.34</x:v>
+        <x:v>30.5</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>25.18</x:v>
+        <x:v>25.2</x:v>
       </x:c>
       <x:c r="J10" s="0">
         <x:v>32.72</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:12">
@@ -924,7 +927,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>101.8</x:v>
+        <x:v>102.4</x:v>
       </x:c>
       <x:c r="E11" s="0">
         <x:v>96.55</x:v>
@@ -945,15 +948,15 @@
         <x:v>130.91</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:12">
       <x:c r="A12" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>13</x:v>
@@ -962,10 +965,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>137.5</x:v>
+        <x:v>136.8</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>120.91</x:v>
+        <x:v>124.76</x:v>
       </x:c>
       <x:c r="F12" s="0">
         <x:v>139.8</x:v>
@@ -983,15 +986,15 @@
         <x:v>163.11</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:12">
       <x:c r="A13" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>13</x:v>
@@ -1000,7 +1003,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>483.25</x:v>
+        <x:v>494.75</x:v>
       </x:c>
       <x:c r="E13" s="0">
         <x:v>465.75</x:v>
@@ -1021,15 +1024,15 @@
         <x:v>566.5</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="L13" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:12">
       <x:c r="A14" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>13</x:v>
@@ -1038,10 +1041,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>14.09</x:v>
+        <x:v>14.18</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>12.72</x:v>
+        <x:v>13.04</x:v>
       </x:c>
       <x:c r="F14" s="0">
         <x:v>14.39</x:v>
@@ -1059,15 +1062,15 @@
         <x:v>17.46</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L14" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:12">
       <x:c r="A15" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>13</x:v>
@@ -1076,7 +1079,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>201.4</x:v>
+        <x:v>200.6</x:v>
       </x:c>
       <x:c r="E15" s="0">
         <x:v>189.5</x:v>
@@ -1097,15 +1100,15 @@
         <x:v>220.84</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="L15" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:12">
       <x:c r="A16" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>13</x:v>
@@ -1114,36 +1117,36 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>34.38</x:v>
+        <x:v>36.9</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>30.84</x:v>
+        <x:v>31.1</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>35.18</x:v>
+        <x:v>37.8</x:v>
       </x:c>
       <x:c r="G16" s="0">
         <x:v>28.26</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>35.18</x:v>
+        <x:v>37.8</x:v>
       </x:c>
       <x:c r="I16" s="0">
         <x:v>27.1</x:v>
       </x:c>
       <x:c r="J16" s="0">
-        <x:v>35.18</x:v>
+        <x:v>37.8</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="L16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:12">
       <x:c r="A17" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>13</x:v>
@@ -1152,19 +1155,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>627.5</x:v>
+        <x:v>647.5</x:v>
       </x:c>
       <x:c r="E17" s="0">
         <x:v>593</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>639.5</x:v>
+        <x:v>647.5</x:v>
       </x:c>
       <x:c r="G17" s="0">
         <x:v>562</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>639.5</x:v>
+        <x:v>647.5</x:v>
       </x:c>
       <x:c r="I17" s="0">
         <x:v>558</x:v>
@@ -1173,15 +1176,15 @@
         <x:v>698.5</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L17" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:12">
       <x:c r="A18" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>13</x:v>
@@ -1190,13 +1193,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>42.76</x:v>
+        <x:v>42.16</x:v>
       </x:c>
       <x:c r="E18" s="0">
         <x:v>40.3</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>46.28</x:v>
+        <x:v>44.06</x:v>
       </x:c>
       <x:c r="G18" s="0">
         <x:v>36.8</x:v>
@@ -1211,10 +1214,10 @@
         <x:v>46.28</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="L18" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:12">
@@ -1228,7 +1231,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>20.8</x:v>
+        <x:v>20.96</x:v>
       </x:c>
       <x:c r="E19" s="0">
         <x:v>19.74</x:v>
@@ -1237,7 +1240,7 @@
         <x:v>22.12</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>17.37</x:v>
+        <x:v>17.63</x:v>
       </x:c>
       <x:c r="H19" s="0">
         <x:v>22.32</x:v>
@@ -1249,15 +1252,15 @@
         <x:v>22.32</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="L19" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:12">
       <x:c r="A20" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>13</x:v>
@@ -1266,7 +1269,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>186</x:v>
+        <x:v>184.7</x:v>
       </x:c>
       <x:c r="E20" s="0">
         <x:v>174.2</x:v>
@@ -1287,10 +1290,10 @@
         <x:v>226.1</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="L20" s="0" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="L20" s="0" t="s">
-        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:12">
@@ -1304,7 +1307,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>96.35</x:v>
+        <x:v>97.4</x:v>
       </x:c>
       <x:c r="E21" s="0">
         <x:v>88.55</x:v>
@@ -1325,10 +1328,10 @@
         <x:v>113.18</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L21" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:12">
@@ -1342,7 +1345,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>2.48</x:v>
+        <x:v>2.46</x:v>
       </x:c>
       <x:c r="E22" s="0">
         <x:v>2.36</x:v>
@@ -1363,10 +1366,10 @@
         <x:v>2.79</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="L22" s="0" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="L22" s="0" t="s">
-        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:12">
@@ -1380,7 +1383,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>46.7</x:v>
+        <x:v>46.46</x:v>
       </x:c>
       <x:c r="E23" s="0">
         <x:v>43.52</x:v>
@@ -1401,10 +1404,10 @@
         <x:v>50.9</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="L23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:12">
@@ -1418,10 +1421,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>344</x:v>
+        <x:v>338.25</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>310</x:v>
+        <x:v>311.75</x:v>
       </x:c>
       <x:c r="F24" s="0">
         <x:v>344</x:v>
@@ -1439,10 +1442,10 @@
         <x:v>369</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L24" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:12">
@@ -1456,7 +1459,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>111.2</x:v>
+        <x:v>112.4</x:v>
       </x:c>
       <x:c r="E25" s="0">
         <x:v>104.5</x:v>
@@ -1477,10 +1480,10 @@
         <x:v>129.6</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L25" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:12">
@@ -1494,10 +1497,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>317</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>291.25</x:v>
+        <x:v>291.75</x:v>
       </x:c>
       <x:c r="F26" s="0">
         <x:v>321</x:v>
@@ -1515,10 +1518,10 @@
         <x:v>352.5</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L26" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:12">
@@ -1532,13 +1535,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>271.25</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>252</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>275.25</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="G27" s="0">
         <x:v>252</x:v>
@@ -1570,13 +1573,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>43.44</x:v>
+        <x:v>43.74</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>41.04</x:v>
+        <x:v>41.5</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>45.58</x:v>
+        <x:v>45.28</x:v>
       </x:c>
       <x:c r="G28" s="0">
         <x:v>40.18</x:v>
@@ -1591,15 +1594,15 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="L28" s="0" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="L28" s="0" t="s">
-        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:12">
       <x:c r="A29" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>13</x:v>
@@ -1608,7 +1611,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>61</x:v>
+        <x:v>61.45</x:v>
       </x:c>
       <x:c r="E29" s="0">
         <x:v>57.2</x:v>
@@ -1629,15 +1632,15 @@
         <x:v>75.65</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L29" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:12">
       <x:c r="A30" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>13</x:v>
@@ -1646,7 +1649,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>251</x:v>
+        <x:v>252.25</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>240.2</x:v>
@@ -1655,27 +1658,27 @@
         <x:v>264.5</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>230.07</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="H30" s="0">
         <x:v>265.75</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>199.61</x:v>
+        <x:v>203.84</x:v>
       </x:c>
       <x:c r="J30" s="0">
         <x:v>266.33</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="L30" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:12">
       <x:c r="A31" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>13</x:v>
@@ -1684,10 +1687,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>33.74</x:v>
+        <x:v>33.52</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>30.26</x:v>
+        <x:v>30.68</x:v>
       </x:c>
       <x:c r="F31" s="0">
         <x:v>34</x:v>
@@ -1696,7 +1699,7 @@
         <x:v>29.88</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>37</x:v>
+        <x:v>36.44</x:v>
       </x:c>
       <x:c r="I31" s="0">
         <x:v>29.88</x:v>
@@ -1705,15 +1708,15 @@
         <x:v>43.06</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L31" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:12">
       <x:c r="A32" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>13</x:v>
@@ -1722,19 +1725,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>37.54</x:v>
+        <x:v>37.46</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>33.44</x:v>
+        <x:v>34.1</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>37.76</x:v>
+        <x:v>37.78</x:v>
       </x:c>
       <x:c r="G32" s="0">
         <x:v>32.26</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>37.76</x:v>
+        <x:v>37.78</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>32.26</x:v>
@@ -1743,10 +1746,10 @@
         <x:v>44.5</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L32" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Destek_Direc_Seviyeleri.xlsx
+++ b/Destek_Direc_Seviyeleri.xlsx
@@ -62,57 +62,66 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>PİVOT ALT | GÜÇLÜ YÜKSELİŞ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4/5 (80%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5/5 (100%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASELS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK YAKIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3/5 (60%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
     <x:t>DİRENÇ YAKIN | GÜÇLÜ YÜKSELİŞ</x:t>
   </x:si>
   <x:si>
-    <x:t>4/5 (80%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5/5 (100%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASELS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASTOR</x:t>
+    <x:t>EKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2/5 (40%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENKAI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FROTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK YAKIN | GÜÇLÜ YÜKSELİŞ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUBRF</x:t>
   </x:si>
   <x:si>
     <x:t>NÖTR | GÜÇLÜ YÜKSELİŞ</x:t>
   </x:si>
   <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DİRENÇ YAKIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3/5 (60%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENKAI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FROTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUBRF</x:t>
-  </x:si>
-  <x:si>
     <x:t>ISCTR</x:t>
   </x:si>
   <x:si>
@@ -122,36 +131,33 @@
     <x:t>KRDMD</x:t>
   </x:si>
   <x:si>
+    <x:t>MGROS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PGSUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK YAKIN | GÜÇLÜ DÜŞÜŞ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1/5 (20%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SASA</x:t>
+  </x:si>
+  <x:si>
     <x:t>PİVOT ÜSTÜ | GÜÇLÜ YÜKSELİŞ</x:t>
   </x:si>
   <x:si>
-    <x:t>MGROS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PİVOT ALT | GÜÇLÜ YÜKSELİŞ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PGSUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PİVOT ALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2/5 (40%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SASA</x:t>
-  </x:si>
-  <x:si>
     <x:t>SISE</x:t>
   </x:si>
   <x:si>
@@ -168,9 +174,6 @@
   </x:si>
   <x:si>
     <x:t>TRALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NÖTR</x:t>
   </x:si>
   <x:si>
     <x:t>TTKOM</x:t>
@@ -585,19 +588,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>17.46</x:v>
+        <x:v>18.54</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>16.56</x:v>
+        <x:v>17.85</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>17.73</x:v>
+        <x:v>19.37</x:v>
       </x:c>
       <x:c r="G2" s="0">
         <x:v>16.15</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>18</x:v>
+        <x:v>19.37</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>15.68</x:v>
@@ -623,19 +626,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>75.15</x:v>
+        <x:v>77.6</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>68.25</x:v>
+        <x:v>75.3</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>76.15</x:v>
+        <x:v>81.1</x:v>
       </x:c>
       <x:c r="G3" s="0">
         <x:v>65.05</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>76.26</x:v>
+        <x:v>81.1</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>65.05</x:v>
@@ -661,25 +664,25 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>375.5</x:v>
+        <x:v>407.25</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>327.75</x:v>
+        <x:v>376.5</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>379</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>314.75</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>379</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>283</x:v>
       </x:c>
       <x:c r="J4" s="0">
-        <x:v>379</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
         <x:v>15</x:v>
@@ -699,22 +702,22 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>209</x:v>
+        <x:v>190.4</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>203</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>215.7</x:v>
+        <x:v>212.2</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>181.6</x:v>
+        <x:v>183.1</x:v>
       </x:c>
       <x:c r="H5" s="0">
         <x:v>215.7</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>138.6</x:v>
+        <x:v>145.6</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>215.7</x:v>
@@ -723,12 +726,12 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:12">
       <x:c r="A6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>13</x:v>
@@ -737,25 +740,25 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>739.5</x:v>
+        <x:v>745</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>683.5</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>741.5</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="G6" s="0">
         <x:v>653</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>741.5</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="I6" s="0">
         <x:v>607.5</x:v>
       </x:c>
       <x:c r="J6" s="0">
-        <x:v>741.5</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
         <x:v>15</x:v>
@@ -766,7 +769,7 @@
     </x:row>
     <x:row r="7" spans="1:12">
       <x:c r="A7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>13</x:v>
@@ -775,28 +778,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>2000</x:v>
+        <x:v>2174</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>1949</x:v>
+        <x:v>1995</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>2066</x:v>
+        <x:v>2200</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>1620</x:v>
+        <x:v>1788</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>2066</x:v>
+        <x:v>2200</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>644</x:v>
+        <x:v>670.5</x:v>
       </x:c>
       <x:c r="J7" s="0">
-        <x:v>2066</x:v>
+        <x:v>2200</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>18</x:v>
@@ -804,7 +807,7 @@
     </x:row>
     <x:row r="8" spans="1:12">
       <x:c r="A8" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>13</x:v>
@@ -813,19 +816,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>20.54</x:v>
+        <x:v>20.98</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>19.12</x:v>
+        <x:v>20.68</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>20.92</x:v>
+        <x:v>21.8</x:v>
       </x:c>
       <x:c r="G8" s="0">
         <x:v>18.86</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>21.5</x:v>
+        <x:v>21.8</x:v>
       </x:c>
       <x:c r="I8" s="0">
         <x:v>18.86</x:v>
@@ -834,15 +837,15 @@
         <x:v>27.12</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:12">
       <x:c r="A9" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>13</x:v>
@@ -851,25 +854,25 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>94.9</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>90.46</x:v>
+        <x:v>95.3</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>96.4</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>87.53</x:v>
+        <x:v>89.24</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>96.4</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>77.07</x:v>
+        <x:v>78.39</x:v>
       </x:c>
       <x:c r="J9" s="0">
-        <x:v>102.34</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
         <x:v>15</x:v>
@@ -880,7 +883,7 @@
     </x:row>
     <x:row r="10" spans="1:12">
       <x:c r="A10" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>13</x:v>
@@ -889,22 +892,22 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>30.46</x:v>
+        <x:v>30.92</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>28.02</x:v>
+        <x:v>30.16</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>30.5</x:v>
+        <x:v>32.44</x:v>
       </x:c>
       <x:c r="G10" s="0">
         <x:v>26.78</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>30.5</x:v>
+        <x:v>32.44</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>25.2</x:v>
+        <x:v>25.96</x:v>
       </x:c>
       <x:c r="J10" s="0">
         <x:v>32.72</x:v>
@@ -913,12 +916,12 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:12">
       <x:c r="A11" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>13</x:v>
@@ -927,19 +930,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>102.4</x:v>
+        <x:v>105.8</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>96.55</x:v>
+        <x:v>102.3</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>102.9</x:v>
+        <x:v>109.2</x:v>
       </x:c>
       <x:c r="G11" s="0">
         <x:v>96.55</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>110.02</x:v>
+        <x:v>109.8</x:v>
       </x:c>
       <x:c r="I11" s="0">
         <x:v>96.55</x:v>
@@ -948,15 +951,15 @@
         <x:v>130.91</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:12">
       <x:c r="A12" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>13</x:v>
@@ -968,16 +971,16 @@
         <x:v>136.8</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>124.76</x:v>
+        <x:v>135.9</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>139.8</x:v>
+        <x:v>144.2</x:v>
       </x:c>
       <x:c r="G12" s="0">
         <x:v>119.86</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>139.8</x:v>
+        <x:v>144.2</x:v>
       </x:c>
       <x:c r="I12" s="0">
         <x:v>119.86</x:v>
@@ -986,15 +989,15 @@
         <x:v>163.11</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:12">
       <x:c r="A13" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>13</x:v>
@@ -1003,28 +1006,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>494.75</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>465.75</x:v>
+        <x:v>478.25</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>508</x:v>
+        <x:v>541.5</x:v>
       </x:c>
       <x:c r="G13" s="0">
         <x:v>447</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>537.5</x:v>
+        <x:v>541.5</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>361.5</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="J13" s="0">
         <x:v>566.5</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="L13" s="0" t="s">
         <x:v>18</x:v>
@@ -1032,7 +1035,7 @@
     </x:row>
     <x:row r="14" spans="1:12">
       <x:c r="A14" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>13</x:v>
@@ -1041,19 +1044,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>14.18</x:v>
+        <x:v>14.35</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>13.04</x:v>
+        <x:v>14.24</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>14.39</x:v>
+        <x:v>15.12</x:v>
       </x:c>
       <x:c r="G14" s="0">
         <x:v>12.38</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>14.39</x:v>
+        <x:v>15.12</x:v>
       </x:c>
       <x:c r="I14" s="0">
         <x:v>12.38</x:v>
@@ -1062,15 +1065,15 @@
         <x:v>17.46</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L14" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:12">
       <x:c r="A15" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>13</x:v>
@@ -1079,19 +1082,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>200.6</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>189.5</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>205.4</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="G15" s="0">
         <x:v>179.49</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>205.4</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="I15" s="0">
         <x:v>172.93</x:v>
@@ -1100,15 +1103,15 @@
         <x:v>220.84</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L15" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:12">
       <x:c r="A16" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>13</x:v>
@@ -1117,28 +1120,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>36.9</x:v>
+        <x:v>35.74</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>31.1</x:v>
+        <x:v>35.22</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>37.8</x:v>
+        <x:v>39.24</x:v>
       </x:c>
       <x:c r="G16" s="0">
         <x:v>28.26</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>37.8</x:v>
+        <x:v>39.24</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>27.1</x:v>
+        <x:v>27.7</x:v>
       </x:c>
       <x:c r="J16" s="0">
-        <x:v>37.8</x:v>
+        <x:v>39.24</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L16" s="0" t="s">
         <x:v>18</x:v>
@@ -1146,7 +1149,7 @@
     </x:row>
     <x:row r="17" spans="1:12">
       <x:c r="A17" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>13</x:v>
@@ -1155,19 +1158,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>647.5</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>593</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>647.5</x:v>
+        <x:v>663.5</x:v>
       </x:c>
       <x:c r="G17" s="0">
         <x:v>562</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>647.5</x:v>
+        <x:v>663.5</x:v>
       </x:c>
       <x:c r="I17" s="0">
         <x:v>558</x:v>
@@ -1176,7 +1179,7 @@
         <x:v>698.5</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="L17" s="0" t="s">
         <x:v>18</x:v>
@@ -1184,7 +1187,7 @@
     </x:row>
     <x:row r="18" spans="1:12">
       <x:c r="A18" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>13</x:v>
@@ -1193,13 +1196,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>42.16</x:v>
+        <x:v>39.44</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>40.3</x:v>
+        <x:v>39.2</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>44.06</x:v>
+        <x:v>43.46</x:v>
       </x:c>
       <x:c r="G18" s="0">
         <x:v>36.8</x:v>
@@ -1214,15 +1217,15 @@
         <x:v>46.28</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="L18" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:12">
       <x:c r="A19" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>13</x:v>
@@ -1231,28 +1234,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>20.96</x:v>
+        <x:v>22.64</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>19.74</x:v>
+        <x:v>21.14</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>22.12</x:v>
+        <x:v>22.96</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>17.63</x:v>
+        <x:v>18.76</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>22.32</x:v>
+        <x:v>22.96</x:v>
       </x:c>
       <x:c r="I19" s="0">
         <x:v>16.5</x:v>
       </x:c>
       <x:c r="J19" s="0">
-        <x:v>22.32</x:v>
+        <x:v>22.96</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="L19" s="0" t="s">
         <x:v>18</x:v>
@@ -1260,7 +1263,7 @@
     </x:row>
     <x:row r="20" spans="1:12">
       <x:c r="A20" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>13</x:v>
@@ -1269,19 +1272,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>184.7</x:v>
+        <x:v>185.4</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>174.2</x:v>
+        <x:v>182.6</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>190.6</x:v>
+        <x:v>191.4</x:v>
       </x:c>
       <x:c r="G20" s="0">
         <x:v>169.1</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>190.6</x:v>
+        <x:v>191.4</x:v>
       </x:c>
       <x:c r="I20" s="0">
         <x:v>167.3</x:v>
@@ -1290,15 +1293,15 @@
         <x:v>226.1</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="L20" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:12">
       <x:c r="A21" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>13</x:v>
@@ -1307,19 +1310,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>97.4</x:v>
+        <x:v>99.1</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>88.55</x:v>
+        <x:v>97.85</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>98.15</x:v>
+        <x:v>102.2</x:v>
       </x:c>
       <x:c r="G21" s="0">
         <x:v>85.92</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>98.15</x:v>
+        <x:v>102.2</x:v>
       </x:c>
       <x:c r="I21" s="0">
         <x:v>84.74</x:v>
@@ -1328,15 +1331,15 @@
         <x:v>113.18</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L21" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:12">
       <x:c r="A22" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>13</x:v>
@@ -1345,36 +1348,36 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>2.46</x:v>
+        <x:v>3.03</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>2.36</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>2.53</x:v>
+        <x:v>3.19</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>2.18</x:v>
+        <x:v>2.29</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>2.62</x:v>
+        <x:v>3.19</x:v>
       </x:c>
       <x:c r="I22" s="0">
         <x:v>2.13</x:v>
       </x:c>
       <x:c r="J22" s="0">
-        <x:v>2.79</x:v>
+        <x:v>3.19</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L22" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:12">
       <x:c r="A23" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>13</x:v>
@@ -1383,36 +1386,36 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>46.46</x:v>
+        <x:v>46.86</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>43.52</x:v>
+        <x:v>46.54</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>47.82</x:v>
+        <x:v>49.14</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>40.92</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H23" s="0">
         <x:v>50.3</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>38.04</x:v>
+        <x:v>38.82</x:v>
       </x:c>
       <x:c r="J23" s="0">
         <x:v>50.9</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L23" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:12">
       <x:c r="A24" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>13</x:v>
@@ -1421,19 +1424,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>338.25</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>311.75</x:v>
+        <x:v>313.25</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>344</x:v>
+        <x:v>349.5</x:v>
       </x:c>
       <x:c r="G24" s="0">
         <x:v>269.25</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>344</x:v>
+        <x:v>349.5</x:v>
       </x:c>
       <x:c r="I24" s="0">
         <x:v>269.25</x:v>
@@ -1442,15 +1445,15 @@
         <x:v>369</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="L24" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:12">
       <x:c r="A25" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>13</x:v>
@@ -1459,28 +1462,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>112.4</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>104.5</x:v>
+        <x:v>112.7</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>113.3</x:v>
+        <x:v>118.5</x:v>
       </x:c>
       <x:c r="G25" s="0">
         <x:v>102.5</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>113.3</x:v>
+        <x:v>118.5</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>100.7</x:v>
+        <x:v>102.5</x:v>
       </x:c>
       <x:c r="J25" s="0">
         <x:v>129.6</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="L25" s="0" t="s">
         <x:v>18</x:v>
@@ -1488,7 +1491,7 @@
     </x:row>
     <x:row r="26" spans="1:12">
       <x:c r="A26" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>13</x:v>
@@ -1497,19 +1500,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>316</x:v>
+        <x:v>316.5</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>291.75</x:v>
+        <x:v>314.25</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>321</x:v>
+        <x:v>326.75</x:v>
       </x:c>
       <x:c r="G26" s="0">
         <x:v>279.5</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>321</x:v>
+        <x:v>326.75</x:v>
       </x:c>
       <x:c r="I26" s="0">
         <x:v>263.5</x:v>
@@ -1518,15 +1521,15 @@
         <x:v>352.5</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L26" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:12">
       <x:c r="A27" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>13</x:v>
@@ -1535,19 +1538,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>276</x:v>
+        <x:v>286.5</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>252</x:v>
+        <x:v>277.75</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>277</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="G27" s="0">
         <x:v>252</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>298.67</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="I27" s="0">
         <x:v>252</x:v>
@@ -1564,7 +1567,7 @@
     </x:row>
     <x:row r="28" spans="1:12">
       <x:c r="A28" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>13</x:v>
@@ -1573,19 +1576,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>43.74</x:v>
+        <x:v>46.2</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>41.5</x:v>
+        <x:v>43.12</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>45.28</x:v>
+        <x:v>48.22</x:v>
       </x:c>
       <x:c r="G28" s="0">
         <x:v>40.18</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>55.75</x:v>
+        <x:v>53.5</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>40.18</x:v>
@@ -1594,15 +1597,15 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L28" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:12">
       <x:c r="A29" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>13</x:v>
@@ -1611,19 +1614,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>61.45</x:v>
+        <x:v>62.8</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>57.2</x:v>
+        <x:v>61.05</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>62.2</x:v>
+        <x:v>64.5</x:v>
       </x:c>
       <x:c r="G29" s="0">
         <x:v>56.8</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>63.7</x:v>
+        <x:v>64.5</x:v>
       </x:c>
       <x:c r="I29" s="0">
         <x:v>56.8</x:v>
@@ -1632,15 +1635,15 @@
         <x:v>75.65</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="L29" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:12">
       <x:c r="A30" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>13</x:v>
@@ -1649,36 +1652,36 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>252.25</x:v>
+        <x:v>266.5</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>240.2</x:v>
+        <x:v>251.75</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>264.5</x:v>
+        <x:v>272.5</x:v>
       </x:c>
       <x:c r="G30" s="0">
         <x:v>234</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>265.75</x:v>
+        <x:v>272.5</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>203.84</x:v>
+        <x:v>204.13</x:v>
       </x:c>
       <x:c r="J30" s="0">
-        <x:v>266.33</x:v>
+        <x:v>272.5</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L30" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:12">
       <x:c r="A31" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>13</x:v>
@@ -1687,19 +1690,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>33.52</x:v>
+        <x:v>33.64</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>30.68</x:v>
+        <x:v>33.56</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>34</x:v>
+        <x:v>35.16</x:v>
       </x:c>
       <x:c r="G31" s="0">
         <x:v>29.88</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>36.44</x:v>
+        <x:v>35.16</x:v>
       </x:c>
       <x:c r="I31" s="0">
         <x:v>29.88</x:v>
@@ -1708,15 +1711,15 @@
         <x:v>43.06</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="L31" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:12">
       <x:c r="A32" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>13</x:v>
@@ -1725,19 +1728,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>37.46</x:v>
+        <x:v>37.34</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>34.1</x:v>
+        <x:v>37.12</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>37.78</x:v>
+        <x:v>39.26</x:v>
       </x:c>
       <x:c r="G32" s="0">
         <x:v>32.26</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>37.78</x:v>
+        <x:v>39.26</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>32.26</x:v>
@@ -1746,10 +1749,10 @@
         <x:v>44.5</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L32" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Destek_Direc_Seviyeleri.xlsx
+++ b/Destek_Direc_Seviyeleri.xlsx
@@ -65,103 +65,103 @@
     <x:t>PİVOT ALT | GÜÇLÜ YÜKSELİŞ</x:t>
   </x:si>
   <x:si>
+    <x:t>5/5 (100%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASELS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK YAKIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3/5 (60%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DİRENÇ YAKIN | GÜÇLÜ YÜKSELİŞ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENKAI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
     <x:t>4/5 (80%)</x:t>
   </x:si>
   <x:si>
-    <x:t>AKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5/5 (100%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASELS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASTOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK YAKIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3/5 (60%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DİRENÇ YAKIN | GÜÇLÜ YÜKSELİŞ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKGYO</x:t>
+    <x:t>FROTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK YAKIN | GÜÇLÜ YÜKSELİŞ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUBRF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NÖTR | GÜÇLÜ YÜKSELİŞ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISCTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MGROS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PGSUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK YAKIN | GÜÇLÜ DÜŞÜŞ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1/5 (20%)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PİVOT ÜSTÜ | GÜÇLÜ YÜKSELİŞ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TAVHL</x:t>
   </x:si>
   <x:si>
     <x:t>2/5 (40%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENKAI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FROTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK YAKIN | GÜÇLÜ YÜKSELİŞ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUBRF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NÖTR | GÜÇLÜ YÜKSELİŞ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISCTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MGROS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PGSUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK YAKIN | GÜÇLÜ DÜŞÜŞ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1/5 (20%)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PİVOT ÜSTÜ | GÜÇLÜ YÜKSELİŞ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TAVHL</x:t>
   </x:si>
   <x:si>
     <x:t>TCELL</x:t>
@@ -588,7 +588,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>18.54</x:v>
+        <x:v>18.56</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>17.85</x:v>
@@ -626,7 +626,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>77.6</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="E3" s="0">
         <x:v>75.3</x:v>
@@ -650,12 +650,12 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:12">
       <x:c r="A4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>13</x:v>
@@ -688,12 +688,12 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:12">
       <x:c r="A5" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>13</x:v>
@@ -702,7 +702,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>190.4</x:v>
+        <x:v>190.6</x:v>
       </x:c>
       <x:c r="E5" s="0">
         <x:v>190</x:v>
@@ -723,15 +723,15 @@
         <x:v>215.7</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L5" s="0" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="L5" s="0" t="s">
-        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:12">
       <x:c r="A6" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>13</x:v>
@@ -740,7 +740,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>745</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>730</x:v>
@@ -764,12 +764,12 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:12">
       <x:c r="A7" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>13</x:v>
@@ -778,7 +778,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>2174</x:v>
+        <x:v>2183</x:v>
       </x:c>
       <x:c r="E7" s="0">
         <x:v>1995</x:v>
@@ -799,15 +799,15 @@
         <x:v>2200</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:12">
       <x:c r="A8" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>13</x:v>
@@ -816,7 +816,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>20.98</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E8" s="0">
         <x:v>20.68</x:v>
@@ -837,15 +837,15 @@
         <x:v>27.12</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="L8" s="0" t="s">
-        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:12">
       <x:c r="A9" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>13</x:v>
@@ -878,12 +878,12 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:12">
       <x:c r="A10" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>13</x:v>
@@ -892,7 +892,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>30.92</x:v>
+        <x:v>30.94</x:v>
       </x:c>
       <x:c r="E10" s="0">
         <x:v>30.16</x:v>
@@ -916,12 +916,12 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:12">
       <x:c r="A11" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>13</x:v>
@@ -930,7 +930,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>105.8</x:v>
+        <x:v>105.9</x:v>
       </x:c>
       <x:c r="E11" s="0">
         <x:v>102.3</x:v>
@@ -954,12 +954,12 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:12">
       <x:c r="A12" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>13</x:v>
@@ -968,7 +968,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>136.8</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E12" s="0">
         <x:v>135.9</x:v>
@@ -989,15 +989,15 @@
         <x:v>163.11</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:12">
       <x:c r="A13" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>13</x:v>
@@ -1006,7 +1006,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>523</x:v>
+        <x:v>522.5</x:v>
       </x:c>
       <x:c r="E13" s="0">
         <x:v>478.25</x:v>
@@ -1027,15 +1027,15 @@
         <x:v>566.5</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="L13" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:12">
       <x:c r="A14" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>13</x:v>
@@ -1044,7 +1044,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>14.35</x:v>
+        <x:v>14.37</x:v>
       </x:c>
       <x:c r="E14" s="0">
         <x:v>14.24</x:v>
@@ -1065,15 +1065,15 @@
         <x:v>17.46</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="L14" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:12">
       <x:c r="A15" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>13</x:v>
@@ -1082,7 +1082,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>203</x:v>
+        <x:v>203.3</x:v>
       </x:c>
       <x:c r="E15" s="0">
         <x:v>199</x:v>
@@ -1106,12 +1106,12 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="L15" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:12">
       <x:c r="A16" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>13</x:v>
@@ -1120,7 +1120,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>35.74</x:v>
+        <x:v>35.78</x:v>
       </x:c>
       <x:c r="E16" s="0">
         <x:v>35.22</x:v>
@@ -1141,15 +1141,15 @@
         <x:v>39.24</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="L16" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:12">
       <x:c r="A17" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>13</x:v>
@@ -1179,15 +1179,15 @@
         <x:v>698.5</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="L17" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:12">
       <x:c r="A18" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>13</x:v>
@@ -1196,7 +1196,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>39.44</x:v>
+        <x:v>39.46</x:v>
       </x:c>
       <x:c r="E18" s="0">
         <x:v>39.2</x:v>
@@ -1217,15 +1217,15 @@
         <x:v>46.28</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L18" s="0" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="L18" s="0" t="s">
-        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:12">
       <x:c r="A19" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>13</x:v>
@@ -1234,7 +1234,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>22.64</x:v>
+        <x:v>22.66</x:v>
       </x:c>
       <x:c r="E19" s="0">
         <x:v>21.14</x:v>
@@ -1255,15 +1255,15 @@
         <x:v>22.96</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="L19" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:12">
       <x:c r="A20" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>13</x:v>
@@ -1293,15 +1293,15 @@
         <x:v>226.1</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="L20" s="0" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="L20" s="0" t="s">
-        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:12">
       <x:c r="A21" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>13</x:v>
@@ -1310,7 +1310,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>99.1</x:v>
+        <x:v>99.25</x:v>
       </x:c>
       <x:c r="E21" s="0">
         <x:v>97.85</x:v>
@@ -1331,7 +1331,7 @@
         <x:v>113.18</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="L21" s="0" t="s">
         <x:v>16</x:v>
@@ -1339,7 +1339,7 @@
     </x:row>
     <x:row r="22" spans="1:12">
       <x:c r="A22" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>13</x:v>
@@ -1348,7 +1348,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>3.03</x:v>
+        <x:v>3.04</x:v>
       </x:c>
       <x:c r="E22" s="0">
         <x:v>2.45</x:v>
@@ -1369,15 +1369,15 @@
         <x:v>3.19</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="L22" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:12">
       <x:c r="A23" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>13</x:v>
@@ -1386,7 +1386,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>46.86</x:v>
+        <x:v>46.9</x:v>
       </x:c>
       <x:c r="E23" s="0">
         <x:v>46.54</x:v>
@@ -1407,15 +1407,15 @@
         <x:v>50.9</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="L23" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:12">
       <x:c r="A24" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>13</x:v>
@@ -1424,7 +1424,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>314</x:v>
+        <x:v>314.5</x:v>
       </x:c>
       <x:c r="E24" s="0">
         <x:v>313.25</x:v>
@@ -1445,10 +1445,10 @@
         <x:v>369</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L24" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:12">
@@ -1483,10 +1483,10 @@
         <x:v>129.6</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="L25" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:12">
@@ -1500,7 +1500,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>316.5</x:v>
+        <x:v>316.75</x:v>
       </x:c>
       <x:c r="E26" s="0">
         <x:v>314.25</x:v>
@@ -1521,10 +1521,10 @@
         <x:v>352.5</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="L26" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:12">
@@ -1538,7 +1538,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>286.5</x:v>
+        <x:v>286.75</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>277.75</x:v>
@@ -1562,7 +1562,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="L27" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:12">
@@ -1576,7 +1576,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>46.2</x:v>
+        <x:v>46.24</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>43.12</x:v>
@@ -1600,7 +1600,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="L28" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:12">
@@ -1635,10 +1635,10 @@
         <x:v>75.65</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="L29" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:12">
@@ -1652,7 +1652,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>266.5</x:v>
+        <x:v>266.75</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>251.75</x:v>
@@ -1673,10 +1673,10 @@
         <x:v>272.5</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="L30" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:12">
@@ -1690,7 +1690,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>33.64</x:v>
+        <x:v>33.66</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>33.56</x:v>
@@ -1711,10 +1711,10 @@
         <x:v>43.06</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L31" s="0" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="L31" s="0" t="s">
-        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:12">
@@ -1749,10 +1749,10 @@
         <x:v>44.5</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="L32" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
